--- a/output/pdf_financials_xlsx/FRNT.xlsx
+++ b/output/pdf_financials_xlsx/FRNT.xlsx
@@ -2711,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.188228</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.188228</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -7011,7 +7011,11 @@
           <t>Warrant reserve 13</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -8133,7 +8137,11 @@
           <t>Warrant reserve 14</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FRNT.xlsx
+++ b/output/pdf_financials_xlsx/FRNT.xlsx
@@ -1418,19 +1418,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.497895</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.403771</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.447314</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.552482</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.399519</v>
       </c>
     </row>
     <row r="35">
@@ -1462,19 +1462,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.497895</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.403771</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.447314</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.552482</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.399519</v>
       </c>
     </row>
     <row r="37">
@@ -1726,19 +1726,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.451959</v>
+        <v>3.954064</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.304166</v>
+        <v>1.900395</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.971714</v>
+        <v>4.5244</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.851008</v>
+        <v>3.298526</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.445901</v>
+        <v>2.046382</v>
       </c>
     </row>
     <row r="49">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/FRNT.xlsx
+++ b/output/pdf_financials_xlsx/FRNT.xlsx
@@ -3111,19 +3111,19 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009161000000000001</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.028582</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.014345</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002135</v>
       </c>
     </row>
     <row r="112">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-0.119109</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -3647,19 +3647,19 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009161000000000001</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.028582</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.014345</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002135</v>
       </c>
     </row>
     <row r="135">
@@ -3669,19 +3669,19 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.7773640000000001</v>
+        <v>-0.786525</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-3.243373</v>
+        <v>-3.271955</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-2.746955</v>
+        <v>-2.7613</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-2.419658</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-2.89126</v>
+        <v>-2.893395</v>
       </c>
     </row>
   </sheetData>
@@ -9785,7 +9785,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="n">
         <v>-0.009161000000000001</v>
       </c>
@@ -11032,7 +11036,11 @@
           <t>Repurchase of shares</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E187" s="5" t="n">
         <v>-0.119109</v>
       </c>
